--- a/Double_FEDs/DOUBLE_FED_weights.xlsx
+++ b/Double_FEDs/DOUBLE_FED_weights.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://api.box.com/wopi/files/2208003664718/WOPIServiceId_TP_BOX_2/WOPIUserId_-/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/murrell_wustl_edu/Documents/Documents/Github/PredictingObesity/Double_FEDs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="109" documentId="13_ncr:1_{D3FBDB76-0A7A-422F-A3F9-0509066F66AC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BF7132B-931F-43DF-AB45-1E54F1E265F7}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9374BD03-A2EF-479B-A78D-7B74FE7CF9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="350" yWindow="640" windowWidth="23230" windowHeight="12880" xr2:uid="{22AD0E44-D2F4-4F54-85C0-7B0E0B24CC5F}"/>
+    <workbookView xWindow="-25620" yWindow="600" windowWidth="23505" windowHeight="13050" xr2:uid="{22AD0E44-D2F4-4F54-85C0-7B0E0B24CC5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
   <si>
     <t>Mouse_ID</t>
   </si>
@@ -87,6 +87,9 @@
   </si>
   <si>
     <t>Change in weight</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Day 4 HFD? </t>
   </si>
 </sst>
 </file>
@@ -479,12 +482,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A11DEB-D9AD-4D05-81DD-C08E314862AA}">
   <dimension ref="A1:L14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="84.6328125" customWidth="1"/>
+    <col min="12" max="12" width="84.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="83.5" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:12" s="1" customFormat="1" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -515,11 +518,14 @@
       <c r="J1" s="1" t="s">
         <v>12</v>
       </c>
+      <c r="K1" s="1" t="s">
+        <v>17</v>
+      </c>
       <c r="L1" s="2" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -550,8 +556,11 @@
       <c r="J2">
         <v>23.03</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K2">
+        <v>20.37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -582,8 +591,11 @@
       <c r="J3">
         <v>22.11</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K3">
+        <v>19.79</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -614,8 +626,11 @@
       <c r="J4">
         <v>21.6</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K4">
+        <v>20.27</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -646,8 +661,11 @@
       <c r="J5">
         <v>22.22</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K5">
+        <v>18.36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -678,8 +696,11 @@
       <c r="J6">
         <v>20.73</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.35">
+      <c r="K6">
+        <v>17.79</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>16</v>
       </c>
@@ -708,7 +729,7 @@
         <v>0.39000000000000057</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E9">
         <f t="shared" ref="E9:J12" si="1">E3-D3</f>
         <v>-0.37000000000000099</v>
@@ -734,7 +755,7 @@
         <v>0.64999999999999858</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E10">
         <f t="shared" si="1"/>
         <v>0.17000000000000171</v>
@@ -760,7 +781,7 @@
         <v>-2.9999999999997584E-2</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E11">
         <f t="shared" si="1"/>
         <v>-0.12000000000000099</v>
@@ -786,7 +807,7 @@
         <v>5.9999999999998721E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E12">
         <f t="shared" si="1"/>
         <v>-0.47999999999999687</v>
@@ -812,29 +833,29 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="E14">
-        <f>AVERAGE(E8:E12)</f>
+        <f t="shared" ref="E14:J14" si="2">AVERAGE(E8:E12)</f>
         <v>-0.39399999999999907</v>
       </c>
       <c r="F14">
-        <f>AVERAGE(F8:F12)</f>
+        <f t="shared" si="2"/>
         <v>0.17199999999999918</v>
       </c>
       <c r="G14">
-        <f>AVERAGE(G8:G12)</f>
+        <f t="shared" si="2"/>
         <v>0.65200000000000036</v>
       </c>
       <c r="H14">
-        <f>AVERAGE(H8:H12)</f>
+        <f t="shared" si="2"/>
         <v>-0.14799999999999969</v>
       </c>
       <c r="I14">
-        <f>AVERAGE(I8:I12)</f>
+        <f t="shared" si="2"/>
         <v>-0.31600000000000039</v>
       </c>
       <c r="J14">
-        <f>AVERAGE(J8:J12)</f>
+        <f t="shared" si="2"/>
         <v>0.36000000000000015</v>
       </c>
     </row>

--- a/Double_FEDs/DOUBLE_FED_weights.xlsx
+++ b/Double_FEDs/DOUBLE_FED_weights.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://gowustl-my.sharepoint.com/personal/murrell_wustl_edu/Documents/Documents/Github/PredictingObesity/Double_FEDs/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{9374BD03-A2EF-479B-A78D-7B74FE7CF9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="26" documentId="8_{9374BD03-A2EF-479B-A78D-7B74FE7CF9EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4CFE46FF-2AA1-410A-9303-BA3C2F8775B3}"/>
   <bookViews>
-    <workbookView xWindow="-25620" yWindow="600" windowWidth="23505" windowHeight="13050" xr2:uid="{22AD0E44-D2F4-4F54-85C0-7B0E0B24CC5F}"/>
+    <workbookView xWindow="-28515" yWindow="2160" windowWidth="23505" windowHeight="13050" xr2:uid="{22AD0E44-D2F4-4F54-85C0-7B0E0B24CC5F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>Mouse_ID</t>
   </si>
@@ -90,6 +90,15 @@
   </si>
   <si>
     <t xml:space="preserve">Day 4 HFD? </t>
+  </si>
+  <si>
+    <t>Day 5 HFD</t>
+  </si>
+  <si>
+    <t>Ear tag</t>
+  </si>
+  <si>
+    <t>359 (none)</t>
   </si>
 </sst>
 </file>
@@ -145,7 +154,7 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -481,385 +490,479 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{98A11DEB-D9AD-4D05-81DD-C08E314862AA}">
-  <dimension ref="A1:L14"/>
+  <dimension ref="A1:M15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="84.5703125" customWidth="1"/>
+    <col min="12" max="12" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" ht="83.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="G1" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+      <c r="L1" s="2"/>
+    </row>
+    <row r="2" spans="1:13" s="1" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B2" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="I1" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
+      <c r="M2" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
         <v>1</v>
       </c>
-      <c r="B2">
+      <c r="B3">
+        <v>358</v>
+      </c>
+      <c r="C3">
         <v>18</v>
       </c>
-      <c r="C2">
+      <c r="D3">
         <v>73</v>
       </c>
-      <c r="D2">
+      <c r="E3">
         <v>23.97</v>
       </c>
-      <c r="E2">
+      <c r="F3">
         <v>22.8</v>
       </c>
-      <c r="F2">
+      <c r="G3">
         <v>23.29</v>
       </c>
-      <c r="G2">
+      <c r="H3">
         <v>22.31</v>
       </c>
-      <c r="H2">
+      <c r="I3">
         <v>22.81</v>
       </c>
-      <c r="I2">
+      <c r="J3">
         <v>22.64</v>
       </c>
-      <c r="J2">
+      <c r="K3">
         <v>23.03</v>
       </c>
-      <c r="K2">
+      <c r="L3">
         <v>20.37</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+      <c r="M3">
+        <v>23.46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
         <v>2</v>
       </c>
-      <c r="B3">
+      <c r="B4" t="s">
+        <v>20</v>
+      </c>
+      <c r="C4">
         <v>75</v>
       </c>
-      <c r="C3">
+      <c r="D4">
         <v>69</v>
       </c>
-      <c r="D3">
+      <c r="E4">
         <v>21.37</v>
       </c>
-      <c r="E3">
+      <c r="F4">
         <v>21</v>
       </c>
-      <c r="F3">
+      <c r="G4">
         <v>21</v>
       </c>
-      <c r="G3">
+      <c r="H4">
         <v>21.78</v>
       </c>
-      <c r="H3">
+      <c r="I4">
         <v>21.57</v>
       </c>
-      <c r="I3">
+      <c r="J4">
         <v>21.46</v>
       </c>
-      <c r="J3">
+      <c r="K4">
         <v>22.11</v>
       </c>
-      <c r="K3">
+      <c r="L4">
         <v>19.79</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+      <c r="M4">
+        <v>23.56</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>3</v>
       </c>
-      <c r="B4">
+      <c r="B5">
+        <v>355</v>
+      </c>
+      <c r="C5">
         <v>67</v>
       </c>
-      <c r="C4">
+      <c r="D5">
         <v>63</v>
       </c>
-      <c r="D4">
+      <c r="E5">
         <v>21</v>
       </c>
-      <c r="E4">
+      <c r="F5">
         <v>21.17</v>
       </c>
-      <c r="F4">
+      <c r="G5">
         <v>21.17</v>
       </c>
-      <c r="G4">
+      <c r="H5">
         <v>22</v>
       </c>
-      <c r="H4">
+      <c r="I5">
         <v>21.73</v>
       </c>
-      <c r="I4">
+      <c r="J5">
         <v>21.63</v>
       </c>
-      <c r="J4">
+      <c r="K5">
         <v>21.6</v>
       </c>
-      <c r="K4">
+      <c r="L5">
         <v>20.27</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
+      <c r="M5">
+        <v>23.9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="B5">
+      <c r="B6">
+        <v>354</v>
+      </c>
+      <c r="C6">
         <v>70</v>
       </c>
-      <c r="C5">
+      <c r="D6">
         <v>72</v>
       </c>
-      <c r="D5">
+      <c r="E6">
         <v>21.82</v>
       </c>
-      <c r="E5">
+      <c r="F6">
         <v>21.7</v>
       </c>
-      <c r="F5">
+      <c r="G6">
         <v>22.02</v>
       </c>
-      <c r="G5">
+      <c r="H6">
         <v>22.34</v>
       </c>
-      <c r="H5">
+      <c r="I6">
         <v>22.26</v>
       </c>
-      <c r="I5">
+      <c r="J6">
         <v>22.16</v>
       </c>
-      <c r="J5">
+      <c r="K6">
         <v>22.22</v>
       </c>
-      <c r="K5">
+      <c r="L6">
         <v>18.36</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
+      <c r="M6">
+        <v>20.22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
         <v>5</v>
       </c>
-      <c r="B6">
+      <c r="B7">
+        <v>353</v>
+      </c>
+      <c r="C7">
         <v>62</v>
       </c>
-      <c r="C6">
+      <c r="D7">
         <v>76</v>
       </c>
-      <c r="D6">
+      <c r="E7">
         <v>19.899999999999999</v>
       </c>
-      <c r="E6">
+      <c r="F7">
         <v>19.420000000000002</v>
       </c>
-      <c r="F6">
+      <c r="G7">
         <v>19.47</v>
       </c>
-      <c r="G6">
+      <c r="H7">
         <v>21.78</v>
       </c>
-      <c r="H6">
+      <c r="I7">
         <v>21.1</v>
       </c>
-      <c r="I6">
+      <c r="J7">
         <v>20</v>
       </c>
-      <c r="J6">
+      <c r="K7">
         <v>20.73</v>
       </c>
-      <c r="K6">
+      <c r="L7">
         <v>17.79</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
+      <c r="M7">
+        <v>19.16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>16</v>
       </c>
-      <c r="E8">
-        <f>E2-D2</f>
+      <c r="F9">
+        <f>F3-E3</f>
         <v>-1.1699999999999982</v>
       </c>
-      <c r="F8">
-        <f t="shared" ref="F8:J8" si="0">F2-E2</f>
+      <c r="G9">
+        <f t="shared" ref="G9:K9" si="0">G3-F3</f>
         <v>0.48999999999999844</v>
       </c>
-      <c r="G8">
+      <c r="H9">
         <f t="shared" si="0"/>
         <v>-0.98000000000000043</v>
       </c>
-      <c r="H8">
+      <c r="I9">
         <f t="shared" si="0"/>
         <v>0.5</v>
       </c>
-      <c r="I8">
+      <c r="J9">
         <f t="shared" si="0"/>
         <v>-0.16999999999999815</v>
       </c>
-      <c r="J8">
+      <c r="K9">
         <f t="shared" si="0"/>
         <v>0.39000000000000057</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E9">
-        <f t="shared" ref="E9:J12" si="1">E3-D3</f>
+      <c r="L9">
+        <f>L3-K3</f>
+        <v>-2.66</v>
+      </c>
+      <c r="M9">
+        <f>M3-L3</f>
+        <v>3.09</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F10">
+        <f t="shared" ref="F10:M13" si="1">F4-E4</f>
         <v>-0.37000000000000099</v>
       </c>
-      <c r="F9">
+      <c r="G10">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G9">
+      <c r="H10">
         <f t="shared" si="1"/>
         <v>0.78000000000000114</v>
       </c>
-      <c r="H9">
+      <c r="I10">
         <f t="shared" si="1"/>
         <v>-0.21000000000000085</v>
       </c>
-      <c r="I9">
+      <c r="J10">
         <f t="shared" si="1"/>
         <v>-0.10999999999999943</v>
       </c>
-      <c r="J9">
+      <c r="K10">
         <f t="shared" si="1"/>
         <v>0.64999999999999858</v>
       </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E10">
+      <c r="L10">
+        <f t="shared" ref="L10:L13" si="2">L4-K4</f>
+        <v>-2.3200000000000003</v>
+      </c>
+      <c r="M10">
+        <f t="shared" si="1"/>
+        <v>3.7699999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F11">
         <f t="shared" si="1"/>
         <v>0.17000000000000171</v>
       </c>
-      <c r="F10">
+      <c r="G11">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
-      <c r="G10">
+      <c r="H11">
         <f t="shared" si="1"/>
         <v>0.82999999999999829</v>
       </c>
-      <c r="H10">
+      <c r="I11">
         <f t="shared" si="1"/>
         <v>-0.26999999999999957</v>
       </c>
-      <c r="I10">
+      <c r="J11">
         <f t="shared" si="1"/>
         <v>-0.10000000000000142</v>
       </c>
-      <c r="J10">
+      <c r="K11">
         <f t="shared" si="1"/>
         <v>-2.9999999999997584E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E11">
+      <c r="L11">
+        <f t="shared" si="2"/>
+        <v>-1.3300000000000018</v>
+      </c>
+      <c r="M11">
+        <f t="shared" si="1"/>
+        <v>3.629999999999999</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F12">
         <f t="shared" si="1"/>
         <v>-0.12000000000000099</v>
       </c>
-      <c r="F11">
+      <c r="G12">
         <f t="shared" si="1"/>
         <v>0.32000000000000028</v>
       </c>
-      <c r="G11">
+      <c r="H12">
         <f t="shared" si="1"/>
         <v>0.32000000000000028</v>
       </c>
-      <c r="H11">
+      <c r="I12">
         <f t="shared" si="1"/>
         <v>-7.9999999999998295E-2</v>
       </c>
-      <c r="I11">
+      <c r="J12">
         <f t="shared" si="1"/>
         <v>-0.10000000000000142</v>
       </c>
-      <c r="J11">
+      <c r="K12">
         <f t="shared" si="1"/>
         <v>5.9999999999998721E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E12">
+      <c r="L12">
+        <f t="shared" si="2"/>
+        <v>-3.8599999999999994</v>
+      </c>
+      <c r="M12">
+        <f t="shared" si="1"/>
+        <v>1.8599999999999994</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F13">
         <f t="shared" si="1"/>
         <v>-0.47999999999999687</v>
       </c>
-      <c r="F12">
+      <c r="G13">
         <f t="shared" si="1"/>
         <v>4.9999999999997158E-2</v>
       </c>
-      <c r="G12">
+      <c r="H13">
         <f t="shared" si="1"/>
         <v>2.3100000000000023</v>
       </c>
-      <c r="H12">
+      <c r="I13">
         <f t="shared" si="1"/>
         <v>-0.67999999999999972</v>
       </c>
-      <c r="I12">
+      <c r="J13">
         <f t="shared" si="1"/>
         <v>-1.1000000000000014</v>
       </c>
-      <c r="J12">
+      <c r="K13">
         <f t="shared" si="1"/>
         <v>0.73000000000000043</v>
       </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="E14">
-        <f t="shared" ref="E14:J14" si="2">AVERAGE(E8:E12)</f>
+      <c r="L13">
+        <f t="shared" si="2"/>
+        <v>-2.9400000000000013</v>
+      </c>
+      <c r="M13">
+        <f t="shared" si="1"/>
+        <v>1.370000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="F15">
+        <f t="shared" ref="F15:K15" si="3">AVERAGE(F9:F13)</f>
         <v>-0.39399999999999907</v>
       </c>
-      <c r="F14">
-        <f t="shared" si="2"/>
+      <c r="G15">
+        <f t="shared" si="3"/>
         <v>0.17199999999999918</v>
       </c>
-      <c r="G14">
-        <f t="shared" si="2"/>
+      <c r="H15">
+        <f t="shared" si="3"/>
         <v>0.65200000000000036</v>
       </c>
-      <c r="H14">
-        <f t="shared" si="2"/>
+      <c r="I15">
+        <f t="shared" si="3"/>
         <v>-0.14799999999999969</v>
       </c>
-      <c r="I14">
-        <f t="shared" si="2"/>
+      <c r="J15">
+        <f t="shared" si="3"/>
         <v>-0.31600000000000039</v>
       </c>
-      <c r="J14">
-        <f t="shared" si="2"/>
+      <c r="K15">
+        <f t="shared" si="3"/>
         <v>0.36000000000000015</v>
       </c>
+      <c r="L15">
+        <f t="shared" ref="L15:M15" si="4">AVERAGE(L9:L13)</f>
+        <v>-2.6220000000000008</v>
+      </c>
+      <c r="M15">
+        <f t="shared" si="4"/>
+        <v>2.7439999999999998</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="G1:L1"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>